--- a/docs/e2e/e2e-test-scenarios-final.xlsx
+++ b/docs/e2e/e2e-test-scenarios-final.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처 매핑" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'시나리오'!$A$1:$U$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'시나리오'!$A$1:$U$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'삭제·병합 내역'!$A$1:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'출처 매핑'!$A$1:$E$222</definedName>
   </definedNames>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U43"/>
+  <dimension ref="A1:U47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4859,10 +4859,415 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>E2E-042</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>3. 경로안 계산·비교</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>비정상 수량으로 시뮬레이션해도 서버 오류 없이 400 으로 거부된다</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>견고성</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>로그인 상태</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>1. POST /api/simulate 에 다음 본문을 차례로 보낸다: Integer 최댓값, 상한(100,000K) 초과, 음수 섞임, 전부 0, 빈 orders·null·본문 없음, 없는 나라(MARS), 문자열·배열 수량, 21자리 정수, 깨진 JSON, 소수 수량(1.5)
+2. 경계값(CHINA 100,000)과 한국(공장 아님) 수량이 섞인 요청을 보낸다</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>1: 모두 400 대 응답과 이유가 돌아온다. 500 이나 스택 트레이스가 없다. (소수 수량 1.5 도 400 이어야 한다)
+2: 200 으로 계산되고, 한국 수량은 무시된다.</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>일부 불일치(수정함)</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>RobustnessTests.simulateRejectsAbnormalQuantitiesWithoutServerError, simulateAcceptsLimitBoundaryAndIgnoresKorea</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R44" s="7" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="T44" s="7" t="inlineStr">
+        <is>
+          <t>장영은</t>
+        </is>
+      </c>
+      <c r="U44" s="6" t="inlineStr">
+        <is>
+          <t>소수 수량 1.5 가 200 으로 처리되던 결함을 JacksonConfig 로 고쳐 400 이 되도록 했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>E2E-043</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>4. 주문 확정</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>깨진 확정·가입·로그인 요청은 거부되고 주문이 생기지 않는다</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>견고성</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>R9, R11</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>8, 14</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>로그인 상태</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>1. POST /api/orders 에 깨진 JSON, masterVersion 누락·문자열, routeType null·없는 값, orders null, 5,000자 고객사명을 보낸다
+2. POST /api/login·/api/signup 에 깨진 JSON, 빈 본문, null 값, 숫자·불리언 값, 100,000자 아이디, 101자 비밀번호를 보낸다</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>1: 모두 4xx 이고 주문 수가 그대로다.
+2: 모두 4xx 로 거부된다. 숫자·불리언 값으로는 계정이 만들어지지 않는다.</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>일부 불일치(수정함)</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>RobustnessTests.malformedRequestsAreRejectedAndCreateNothing</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R45" s="7" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="T45" s="7" t="inlineStr">
+        <is>
+          <t>장영은</t>
+        </is>
+      </c>
+      <c r="U45" s="6" t="inlineStr">
+        <is>
+          <t>숫자·불리언 아이디·비밀번호로 200 가입되던 결함을 JacksonConfig 로 고쳐 400 이 되도록 했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>E2E-044</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>4. 주문 확정</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>같은 화면에서 동시에 여러 번 확정해도 성공한 만큼만 주문이 생긴다</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>견고성</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>R5, R9</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>2, 8</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>로그인 상태, 마스터 초기값</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>1. 시뮬레이션으로 마스터 버전을 얻는다
+2. 같은 본문으로 POST /api/orders 를 8개 스레드에서 동시에 보낸다</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>모든 응답이 200 또는 409 이다. 성공한 응답의 주문 번호가 겹치지 않고, 늘어난 주문 수가 성공 횟수와 같다.</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>일치 예상</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>RobustnessTests.concurrentConfirmsCreateExactlyAsManyOrdersAsSucceeded</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R46" s="7" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="T46" s="7" t="inlineStr">
+        <is>
+          <t>장영은</t>
+        </is>
+      </c>
+      <c r="U46" s="6" t="inlineStr">
+        <is>
+          <t>같은 요청을 연속으로 보내면 주문이 여러 건 생기는 것은 허용된 동작으로 보고 검증하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>E2E-045</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>6. 주문 상태 관리</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>상태·고객사 변경 API 에 잘못된 값을 보내도 거부되고 상태가 그대로다</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>견고성</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>로그인 상태, 확정 주문 1건</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>1. POST /api/orders/{id}/status 에 없는 상태값, version 문자열·음수·21자리 정수, 배열, 깨진 본문, status null·누락을 보낸다
+2. 없는 주문 번호, 숫자가 아닌 주문 번호로 보낸다
+3. POST /api/orders/{id}/customer 에 5,000자 고객사명을 보낸다
+4. 주문 상세를 조회한다</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>1~3: 모두 4xx 이다. status null·누락도 500 이 아니라 400 이어야 한다.
+4: 상태는 '확정' 그대로다.</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>일부 불일치(수정함)</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="n"/>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>RobustnessTests.statusAndCustomerUpdatesRejectInvalidInput</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R47" s="7" t="inlineStr">
+        <is>
+          <t>통과</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="T47" s="7" t="inlineStr">
+        <is>
+          <t>장영은</t>
+        </is>
+      </c>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>status 가 null·누락일 때 500 이던 결함을 OrderService.changeStatus 의 null 검사로 고쳐 400 이 되도록 했다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U43"/>
+  <autoFilter ref="A1:U47"/>
   <dataValidations count="1">
-    <dataValidation sqref="R2:R43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="R2:R47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"미실행,통과,실패,보류"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4952,7 +5357,7 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTA(시나리오!$A$2:$A$43)</f>
+        <f>COUNTA(시나리오!$A$2:$A$47)</f>
         <v/>
       </c>
     </row>
@@ -5008,19 +5413,19 @@
         </is>
       </c>
       <c r="B13" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A13)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A13)</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A13,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A13,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A13,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A13,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E13" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A13,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A13,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5031,19 +5436,19 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A14)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A14)</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A14,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A14,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A14,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A14,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A14,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A14,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5054,19 +5459,19 @@
         </is>
       </c>
       <c r="B15" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A15)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A15)</f>
         <v/>
       </c>
       <c r="C15" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A15,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A15,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D15" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A15,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A15,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E15" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A15,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A15,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5077,19 +5482,19 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A16)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A16)</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A16,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A16,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A16,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A16,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A16,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A16,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5100,19 +5505,19 @@
         </is>
       </c>
       <c r="B17" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A17)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A17)</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A17,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A17,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D17" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A17,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A17,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E17" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A17,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A17,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5123,19 +5528,19 @@
         </is>
       </c>
       <c r="B18" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A18)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A18)</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A18,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A18,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D18" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A18,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A18,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E18" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A18,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A18,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5146,19 +5551,19 @@
         </is>
       </c>
       <c r="B19" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A19)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A19)</f>
         <v/>
       </c>
       <c r="C19" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A19,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A19,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D19" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A19,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A19,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E19" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A19,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A19,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5169,19 +5574,19 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>COUNTIF(시나리오!$C$2:$C$43,A20)</f>
+        <f>COUNTIF(시나리오!$C$2:$C$47,A20)</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A20,시나리오!$E$2:$E$43,"상")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A20,시나리오!$E$2:$E$47,"상")</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A20,시나리오!$E$2:$E$43,"중")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A20,시나리오!$E$2:$E$47,"중")</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>COUNTIFS(시나리오!$C$2:$C$43,$A20,시나리오!$E$2:$E$43,"하")</f>
+        <f>COUNTIFS(시나리오!$C$2:$C$47,$A20,시나리오!$E$2:$E$47,"하")</f>
         <v/>
       </c>
     </row>
@@ -5234,7 +5639,7 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$43,A25)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$47,A25)</f>
         <v/>
       </c>
     </row>
@@ -5245,7 +5650,7 @@
         </is>
       </c>
       <c r="B26" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$43,A26)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$47,A26)</f>
         <v/>
       </c>
     </row>
@@ -5256,7 +5661,7 @@
         </is>
       </c>
       <c r="B27" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$43,A27)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$47,A27)</f>
         <v/>
       </c>
     </row>
@@ -5267,7 +5672,7 @@
         </is>
       </c>
       <c r="B28" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$43,A28)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$47,A28)</f>
         <v/>
       </c>
     </row>
@@ -5278,7 +5683,7 @@
         </is>
       </c>
       <c r="B29" s="14">
-        <f>COUNTIF(시나리오!$L$2:$L$43,A29)</f>
+        <f>COUNTIF(시나리오!$L$2:$L$47,A29)</f>
         <v/>
       </c>
     </row>
@@ -5308,7 +5713,7 @@
         </is>
       </c>
       <c r="B33" s="14">
-        <f>COUNTIF(시나리오!$N$2:$N$43,"Y")</f>
+        <f>COUNTIF(시나리오!$N$2:$N$47,"Y")</f>
         <v/>
       </c>
     </row>
@@ -5319,7 +5724,7 @@
         </is>
       </c>
       <c r="B34" s="14">
-        <f>COUNTIF(시나리오!$N$2:$N$43,"N")</f>
+        <f>COUNTIF(시나리오!$N$2:$N$47,"N")</f>
         <v/>
       </c>
     </row>
@@ -5330,7 +5735,7 @@
         </is>
       </c>
       <c r="B35" s="14">
-        <f>COUNTA(시나리오!$O$2:$O$43)</f>
+        <f>COUNTA(시나리오!$O$2:$O$47)</f>
         <v/>
       </c>
     </row>
@@ -5360,7 +5765,7 @@
         </is>
       </c>
       <c r="B39" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$43,A39)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$47,A39)</f>
         <v/>
       </c>
     </row>
@@ -5371,7 +5776,7 @@
         </is>
       </c>
       <c r="B40" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$43,A40)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$47,A40)</f>
         <v/>
       </c>
     </row>
@@ -5382,7 +5787,7 @@
         </is>
       </c>
       <c r="B41" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$43,A41)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$47,A41)</f>
         <v/>
       </c>
     </row>
@@ -5393,7 +5798,7 @@
         </is>
       </c>
       <c r="B42" s="14">
-        <f>COUNTIF(시나리오!$R$2:$R$43,A42)</f>
+        <f>COUNTIF(시나리오!$R$2:$R$47,A42)</f>
         <v/>
       </c>
     </row>
